--- a/request_forms/050_remark_request_form--request_forms.xlsx
+++ b/request_forms/050_remark_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1216,17 +1216,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>instructor_name_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>smith,_john</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Smith, John</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1272,29 +1272,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>reopened</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Reopened</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>remarker_name_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reopened</t>
+          <t>doe,_jane</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reopened</t>
+          <t>Doe, Jane</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>doe,_jane</t>
+          <t>johnson,_jane</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Doe, Jane</t>
+          <t>Johnson, Jane</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>johnson,_jane</t>
+          <t>smith,_john</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Johnson, Jane</t>
+          <t>Smith, John</t>
         </is>
       </c>
     </row>
@@ -1340,29 +1340,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>smith,_john</t>
+          <t>smith,_jane</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Smith, John</t>
+          <t>Smith, Jane</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>remarker_name_choices</t>
+          <t>remarker_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>smith,_jane</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Smith, Jane</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1391,29 +1391,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>remarker_status_choices</t>
+          <t>created_by_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>doe,_jane</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Doe, Jane</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>doe,_jane</t>
+          <t>johnson,_jane</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Doe, Jane</t>
+          <t>Johnson, Jane</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>johnson,_jane</t>
+          <t>smith,_john</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Johnson, Jane</t>
+          <t>Smith, John</t>
         </is>
       </c>
     </row>
@@ -1459,29 +1459,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>smith,_john</t>
+          <t>smith,_jane</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Smith, John</t>
+          <t>Smith, Jane</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>created_by_choices</t>
+          <t>modified_by_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>smith,_jane</t>
+          <t>doe,_jane</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Smith, Jane</t>
+          <t>Doe, Jane</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>doe,_jane</t>
+          <t>johnson,_jane</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Doe, Jane</t>
+          <t>Johnson, Jane</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>johnson,_jane</t>
+          <t>smith,_john</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Johnson, Jane</t>
+          <t>Smith, John</t>
         </is>
       </c>
     </row>
@@ -1527,27 +1527,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>smith,_john</t>
+          <t>smith,_jane</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Smith, John</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>modified_by_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>smith,_jane</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Smith, Jane</t>
         </is>
